--- a/data/trans_orig/IP16A05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A05-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31677</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12686</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25398</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31458</t>
+          <t>31464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22194</t>
+          <t>21534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38880</t>
+          <t>38759</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45940</t>
+          <t>46022</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>29438</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37075</t>
+          <t>36718</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51386</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60490</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>34355</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108164</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118860</t>
+          <t>118705</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122535</t>
+          <t>122970</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>134127</t>
+          <t>134438</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234741</t>
+          <t>234869</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>250734</t>
+          <t>251633</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>39658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46479</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23889</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32807</t>
+          <t>32879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18475</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24241</t>
+          <t>24168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31940</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24645</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>20068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>18499</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41259</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49409</t>
+          <t>49587</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13304</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30315</t>
+          <t>30259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38601</t>
+          <t>38775</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28216</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58313</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113467</t>
+          <t>113328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128752</t>
+          <t>128551</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129750</t>
+          <t>128442</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143967</t>
+          <t>143604</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>247354</t>
+          <t>246860</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268237</t>
+          <t>268895</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18055</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27947</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35024</t>
+          <t>34621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>42858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21858</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46079</t>
+          <t>46195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19174</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>42498</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>40249</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105900</t>
+          <t>106783</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117615</t>
+          <t>117900</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>99948</t>
+          <t>99360</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>113083</t>
+          <t>112829</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>209885</t>
+          <t>210488</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>226989</t>
+          <t>227854</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29533</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37473</t>
+          <t>38533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51377</t>
+          <t>51268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58868</t>
+          <t>58535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47765</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104421</t>
+          <t>104621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110725</t>
+          <t>110813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34625</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42791</t>
+          <t>42620</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55822</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67250</t>
+          <t>67284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,75%</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>36075</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>151778</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>169671</t>
+          <t>169731</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>165125</t>
+          <t>165638</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>176424</t>
+          <t>176747</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>324139</t>
+          <t>323841</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>342924</t>
+          <t>343685</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
